--- a/justificativas.xlsx
+++ b/justificativas.xlsx
@@ -484,12 +484,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mikeias de Lima Lopes</t>
+          <t>Dhiovana Marques Bavosa Feitosa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>11058</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -499,12 +499,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Teste de func</t>
+          <t>Fui rebelde e não quis registrar meus pontos</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -529,12 +529,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Raposo Tavares</t>
+          <t>Mirian Nascimento</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>11053</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -579,12 +579,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>teste de funcionalidade</t>
+          <t>Teste</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Reprovado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -604,37 +604,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mikeias de Lima Lopes</t>
+          <t>Adriano Saraiva</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Reprovado</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
